--- a/output/tables/univariable_logistic_regression_results.xlsx
+++ b/output/tables/univariable_logistic_regression_results.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -710,34 +710,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Microvascular_flox_index</t>
+          <t>rate_of_reoxygenation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.53, 1.43</t>
+          <t>0.76, 1.28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>&gt;0.9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Peak StO2 post vascular occlusion (%)</t>
+          <t>peak_StO2_post_vascular_occlusion</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -758,6 +758,33 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Microvascular_flox_index</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.53, 1.43</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.6</t>
         </is>
       </c>
     </row>
@@ -768,7 +795,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -801,7 +828,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -867,17 +894,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.80, 1.10</t>
+          <t>0.81, 1.12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
@@ -960,12 +987,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.00, 1.05</t>
+          <t>1.00, 1.06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.033</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1031,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.55, 1.55</t>
+          <t>0.57, 1.49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -1021,17 +1048,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.99, 1.21</t>
+          <t>0.98, 1.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>0.091</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1070,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.10, 31.7</t>
+          <t>0.09, 29.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1060,22 +1087,66 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>rate_of_reoxygenation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.76, 1.30</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Baseline_StO2_level</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>0.96, 1.00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.068</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>peak_StO2_post_vascular_occlusion</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.97, 1.01</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -1294,51 +1365,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lungs</t>
+          <t>Lungs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.24, 4.21</t>
+          <t>0.57, 4.75</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>&gt;0.9</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lungs</t>
+          <t>Renal tract</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.57, 4.75</t>
+          <t>0.24, 4.21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>&gt;0.9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Renal tract</t>
+          <t>Tonsils</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1360,7 +1431,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tonsils</t>
+          <t>Unsure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1382,29 +1453,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>un-specified</t>
+          <t>Urinary tract</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.24, 4.21</t>
+          <t>0.65, 11.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>&gt;0.9</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>Urine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1414,7 +1485,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.29, 3.47</t>
+          <t>0.24, 4.21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1426,7 +1497,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unsure</t>
+          <t>lungs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1448,29 +1519,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Urinary tract</t>
+          <t>un-specified</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.65, 11.5</t>
+          <t>0.24, 4.21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>&gt;0.9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Urine</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1480,7 +1551,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.24, 4.21</t>
+          <t>0.29, 3.47</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1492,7 +1563,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Patient Sex</t>
+          <t>Patient_Sex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1704,7 +1775,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Frailty Score</t>
+          <t>Frailty_Score</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1785,7 +1856,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Chronic Kidney Disease</t>
+          <t>Chronic_Kidney_Disease</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1812,7 +1883,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Chronic Respiratory Disease</t>
+          <t>Chronic_Respiratory_Disease</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1839,7 +1910,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cardiovascular Disease</t>
+          <t>Cardiovascular_Disease</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1866,7 +1937,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Peripheral Vascular Disease</t>
+          <t>Peripheral_Vascular_Disease</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1893,7 +1964,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cancer Diagnosis</t>
+          <t>Cancer_Diagnosis</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1920,7 +1991,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Chronic Liver Disease</t>
+          <t>Chronic_Liver_Disease</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1947,7 +2018,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Chronic Neurological Disease</t>
+          <t>Chronic_Neurological_Disease</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3199,7 +3270,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cholangitis</t>
+          <t>COPD</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3209,7 +3280,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0.30, 3.28</t>
+          <t>0.25, 3.94</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3221,7 +3292,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>COPD</t>
+          <t>Cholangitis</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3231,7 +3302,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0.25, 3.94</t>
+          <t>0.30, 3.28</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
